--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:06:47+00:00</t>
+    <t>2026-09-21T07:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:30:27+00:00</t>
+    <t>2026-09-21T07:49:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:49:30+00:00</t>
+    <t>2026-09-21T07:54:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:54:52+00:00</t>
+    <t>2026-09-21T08:04:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T08:04:47+00:00</t>
+    <t>2026-10-14T09:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T09:34:21+00:00</t>
+    <t>2026-10-15T08:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:56:04+00:00</t>
+    <t>2026-10-15T09:21:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:21:11+00:00</t>
+    <t>2026-10-15T12:03:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:03:42+00:00</t>
+    <t>2026-10-15T12:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Typ av CareTeam</t>
+    <t>Urval typ av CareTeam</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T12:49:20+00:00</t>
+    <t>2026-10-15T13:32:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:32:05+00:00</t>
+    <t>2026-10-15T13:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:47:34+00:00</t>
+    <t>2026-10-15T13:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:54:27+00:00</t>
+    <t>2026-10-15T14:04:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
+++ b/branches/feature-careteam/ValueSet-typ-av-careteam-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T14:04:45+00:00</t>
+    <t>2026-10-28T12:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
